--- a/business_forms/050_customer_loyalty_portal_access_form--business_forms.xlsx
+++ b/business_forms/050_customer_loyalty_portal_access_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -730,12 +730,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="47" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'canada'}</t>
+          <t>canada</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Canada'}</t>
+          <t>Canada</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'united_states'}</t>
+          <t>united_states</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'United States'}</t>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'mexico'}</t>
+          <t>mexico</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Mexico'}</t>
+          <t>Mexico</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'germany'}</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Germany'}</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'australia'}</t>
+          <t>australia</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Australia'}</t>
+          <t>Australia</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'united_kingdom'}</t>
+          <t>united_kingdom</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'United Kingdom'}</t>
+          <t>United Kingdom</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'france'}</t>
+          <t>france</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'France'}</t>
+          <t>France</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'japan'}</t>
+          <t>japan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Japan'}</t>
+          <t>Japan</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'china'}</t>
+          <t>china</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'China'}</t>
+          <t>China</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'spain'}</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Spain'}</t>
+          <t>Spain</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'italy'}</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Italy'}</t>
+          <t>Italy</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'brazil'}</t>
+          <t>brazil</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Brazil'}</t>
+          <t>Brazil</t>
         </is>
       </c>
     </row>
@@ -967,12 +967,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'india'}</t>
+          <t>india</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'India'}</t>
+          <t>India</t>
         </is>
       </c>
     </row>
@@ -984,12 +984,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'south_africa'}</t>
+          <t>south_africa</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'South Africa'}</t>
+          <t>South Africa</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'poland'}</t>
+          <t>poland</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Poland'}</t>
+          <t>Poland</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'netherlands'}</t>
+          <t>netherlands</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Netherlands'}</t>
+          <t>Netherlands</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'south_korea'}</t>
+          <t>south_korea</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'South Korea'}</t>
+          <t>South Korea</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'portugal'}</t>
+          <t>portugal</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Portugal'}</t>
+          <t>Portugal</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'sweden'}</t>
+          <t>sweden</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Sweden'}</t>
+          <t>Sweden</t>
         </is>
       </c>
     </row>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'russia'}</t>
+          <t>russia</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Russia'}</t>
+          <t>Russia</t>
         </is>
       </c>
     </row>
@@ -1103,29 +1103,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'israel'}</t>
+          <t>israel</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Israel'}</t>
+          <t>Israel</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>customer_loyalty_portal_access_form_6_choices</t>
+          <t>customer_loyalty_portal_access_form_7_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'south_korea'}</t>
+          <t>loyalty_program_1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'South Korea'}</t>
+          <t>Loyalty Program 1</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'loyalty_program_1'}</t>
+          <t>loyalty_program_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Loyalty Program 1'}</t>
+          <t>Loyalty Program 2</t>
         </is>
       </c>
     </row>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'loyalty_program_2'}</t>
+          <t>loyalty_program_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Loyalty Program 2'}</t>
+          <t>Loyalty Program 3</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'loyalty_program_3'}</t>
+          <t>loyalty_program_4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Loyalty Program 3'}</t>
+          <t>Loyalty Program 4</t>
         </is>
       </c>
     </row>
@@ -1188,29 +1188,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'loyalty_program_4'}</t>
+          <t>loyalty_program_5</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Loyalty Program 4'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>customer_loyalty_portal_access_form_7_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>{'label':_'loyalty_program_5'}</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>{'label': 'Loyalty Program 5'}</t>
+          <t>Loyalty Program 5</t>
         </is>
       </c>
     </row>
